--- a/Excel Analysis/Vinaysharma_Q1_Solution.xlsx
+++ b/Excel Analysis/Vinaysharma_Q1_Solution.xlsx
@@ -1,215 +1,70 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\Solution of internship work\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD69AD88-44D7-4181-9E3D-DFA8D102CB10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Input_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Calculations" sheetId="2" r:id="rId2"/>
-    <sheet name="Final_Output" sheetId="3" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Input_Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calculations" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final_Output" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="qEaLtqRQ1MZQE7H003s85u8W2GoYx3ACWL7TsTvR2BQ="/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
-  <si>
-    <t>SKU</t>
-  </si>
-  <si>
-    <t>Dimentions ( L X B X H) Inches</t>
-  </si>
-  <si>
-    <t>Weight ( Pounds)</t>
-  </si>
-  <si>
-    <t>MH-107</t>
-  </si>
-  <si>
-    <t>20.5 X 20.5 X 7</t>
-  </si>
-  <si>
-    <t>MH-901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 X 18.5 X 6.25 </t>
-  </si>
-  <si>
-    <t>MH-805</t>
-  </si>
-  <si>
-    <t>23 X 22.75 X 4.75</t>
-  </si>
-  <si>
-    <t>MH-11500</t>
-  </si>
-  <si>
-    <t>18 X 81 X 14.5</t>
-  </si>
-  <si>
-    <t>Expenses involved in selling</t>
-  </si>
-  <si>
-    <t>Channel Commison</t>
-  </si>
-  <si>
-    <t>Storage (Needs to be calculated for 3 month)</t>
-  </si>
-  <si>
-    <t>2$ Per Cubic Meter per month</t>
-  </si>
-  <si>
-    <t>Clossing fee per order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5$ for order value below 120$ and 10$ for orders above 120$ </t>
-  </si>
-  <si>
-    <t>Returns</t>
-  </si>
-  <si>
-    <t>10% of revenue</t>
-  </si>
-  <si>
-    <t>Selling price</t>
-  </si>
-  <si>
-    <t>Selling Price</t>
-  </si>
-  <si>
-    <t>Length(in)</t>
-  </si>
-  <si>
-    <t>Height(in)</t>
-  </si>
-  <si>
-    <t>Height(m)</t>
-  </si>
-  <si>
-    <t>Length(m)</t>
-  </si>
-  <si>
-    <r>
-      <t>Volume(m</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>Storage Cost</t>
-  </si>
-  <si>
-    <t>Commission</t>
-  </si>
-  <si>
-    <t>Closing Fee</t>
-  </si>
-  <si>
-    <t>Breadth(in)</t>
-  </si>
-  <si>
-    <t>Breadth(m)</t>
-  </si>
-  <si>
-    <t>Buying Price</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="6">
     <font>
+      <name val="Aptos Narrow"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
     </font>
     <font>
+      <name val="Aptos Narrow"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
     </font>
     <font>
-      <strike/>
+      <name val="Aptos Narrow"/>
+      <strike val="1"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
     </font>
     <font>
+      <name val="Aptos Narrow"/>
       <sz val="11"/>
-      <name val="Aptos Narrow"/>
     </font>
     <font>
+      <name val="Aptos Narrow"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <vertAlign val="superscript"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -303,157 +158,166 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="3152775" cy="1409700"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Shape 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3769613" y="3075150"/>
-          <a:ext cx="3152775" cy="1409700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cap="flat" cmpd="sng">
-          <a:solidFill>
-            <a:srgbClr val="BABABA"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:round/>
-          <a:headEnd type="none" w="sm" len="sm"/>
-          <a:tailEnd type="none" w="sm" len="sm"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="45700" rIns="91425" bIns="45700" anchor="t" anchorCtr="0">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:buNone/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="Arial"/>
-              <a:cs typeface="Arial"/>
-              <a:sym typeface="Arial"/>
-            </a:rPr>
-            <a:t>Calculate the buying</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="Arial"/>
-              <a:cs typeface="Arial"/>
-              <a:sym typeface="Arial"/>
-            </a:rPr>
-            <a:t> price of the SKU if we are selling these SKUs with Net margin of 15% </a:t>
-          </a:r>
-          <a:endParaRPr sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -653,124 +517,168 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1000"/>
-  <sheetFormatPr defaultColWidth="12.58203125" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.58203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="2" width="53.58203125" customWidth="1"/>
-    <col min="3" max="3" width="27.75" customWidth="1"/>
-    <col min="4" max="4" width="16.1640625" customWidth="1"/>
-    <col min="5" max="26" width="8.58203125" customWidth="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="53.58203125" customWidth="1" min="2" max="2"/>
+    <col width="27.75" customWidth="1" min="3" max="3"/>
+    <col width="16.1640625" customWidth="1" min="4" max="4"/>
+    <col width="8.58203125" customWidth="1" min="5" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
+    <row r="1" ht="14" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Selling price</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Dimensions ( L X B X H) Inches</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Weight ( Pounds)</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="14">
-      <c r="A2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="5">
+    <row r="2" ht="14" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>MH-107</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="6">
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>20.5 X 20.5 X 7</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="14">
-      <c r="A3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="5">
+    <row r="3" ht="14" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>MH-901</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="6">
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30 X 18.5 X 6.25 </t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n">
         <v>20.5</v>
       </c>
-      <c r="E3" s="7"/>
+      <c r="E3" s="7" t="n"/>
     </row>
-    <row r="4" spans="1:5" ht="14">
-      <c r="A4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="5">
+    <row r="4" ht="14" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>MH-805</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
         <v>20.5</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="6">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>23 X 22.75 X 4.75</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
         <v>14.5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="14">
-      <c r="A5" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="9">
+    <row r="5" ht="14" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>MH-11500</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
         <v>163</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="10">
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>18 X 81 X 14.5</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="n">
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="14">
-      <c r="A11" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="15"/>
+    <row r="11" ht="14" customHeight="1">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>Expenses involved in selling</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="n"/>
     </row>
-    <row r="12" spans="1:5" ht="14">
-      <c r="A12" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="11">
+    <row r="12" ht="14" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Channel Commison</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
         <v>0.15</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="14">
-      <c r="A13" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>14</v>
+    <row r="13" ht="14" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Storage (Needs to be calculated for 3 month)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>2$ Per Cubic Meter per month</t>
+        </is>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="14">
-      <c r="A14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>16</v>
+    <row r="14" ht="14" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Clossing fee per order</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5$ for order value below 120$ and 10$ for orders above 120$ </t>
+        </is>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="14">
-      <c r="A15" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>18</v>
+    <row r="15" ht="14" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Returns</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>10% of revenue</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -1759,364 +1667,347 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14E598C3-AFDE-4B32-86D9-DC149DC842F5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="9.75" customWidth="1"/>
-    <col min="2" max="2" width="11.08203125" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" customWidth="1"/>
-    <col min="4" max="4" width="10.5" customWidth="1"/>
-    <col min="7" max="7" width="10.5" customWidth="1"/>
-    <col min="9" max="9" width="11.83203125" customWidth="1"/>
-    <col min="10" max="10" width="11.75" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" customWidth="1"/>
-    <col min="13" max="13" width="10.9140625" customWidth="1"/>
+    <col width="9.75" customWidth="1" min="1" max="1"/>
+    <col width="11.08203125" customWidth="1" min="2" max="2"/>
+    <col width="10.1640625" customWidth="1" min="3" max="3"/>
+    <col width="10.5" customWidth="1" min="4" max="4"/>
+    <col width="10.5" customWidth="1" min="7" max="7"/>
+    <col width="11.83203125" customWidth="1" min="9" max="9"/>
+    <col width="11.75" customWidth="1" min="10" max="10"/>
+    <col width="10.83203125" customWidth="1" min="11" max="11"/>
+    <col width="10.9140625" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="16.5">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" t="s">
+    <row r="1" ht="16.5" customHeight="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Selling Price</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Length(in)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Breadth(in)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Height(in)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Length(m)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Breadth(m)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Height(m)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Volume(m3)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Storage Cost</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Commission</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Returns</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Closing Fee</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <f>Input_Data!A2</f>
+        <v/>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.5207000000000001</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5207000000000001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.1778</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.048206645522</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.289239873132</v>
+      </c>
+      <c r="K2" t="n">
+        <v>15</v>
+      </c>
+      <c r="L2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <f>Input_Data!A3</f>
+        <v/>
+      </c>
+      <c r="B3" t="n">
+        <v>150</v>
+      </c>
+      <c r="C3" t="n">
         <v>30</v>
       </c>
-      <c r="H1" t="s">
+      <c r="D3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.4699</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.15875</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.05684262825</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.3410557695</v>
+      </c>
+      <c r="K3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>15</v>
+      </c>
+      <c r="M3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <f>Input_Data!A4</f>
+        <v/>
+      </c>
+      <c r="B4" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="C4" t="n">
         <v>23</v>
       </c>
-      <c r="I1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J1" t="s">
-        <v>26</v>
-      </c>
-      <c r="K1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M1" t="s">
-        <v>28</v>
+      <c r="D4" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5842000000000001</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.57785</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.12065</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0407290233805</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.244374140283</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.075</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="str">
-        <f>Input_Data!A2</f>
-        <v>MH-107</v>
-      </c>
-      <c r="B2">
-        <f>Input_Data!B2</f>
-        <v>100</v>
-      </c>
-      <c r="C2">
-        <f>VALUE(LEFT(Input_Data!C2,FIND(" X ",Input_Data!C2)-1))</f>
-        <v>20.5</v>
-      </c>
-      <c r="D2">
-        <f>VALUE(MID(Input_Data!C2,FIND(" X ",Input_Data!C2)+3,FIND(" X ",Input_Data!C2,FIND(" X ", Input_Data!C2)+1)-FIND(" X ", Input_Data!C2)-3))</f>
-        <v>20.5</v>
-      </c>
-      <c r="E2">
-        <f>VALUE(RIGHT(Input_Data!C2,LEN(Input_Data!C2)-FIND(" X ", Input_Data!C2,FIND(" X ", Input_Data!C2)+1)-2))</f>
-        <v>7</v>
-      </c>
-      <c r="F2">
-        <f>C2*0.0254</f>
-        <v>0.52069999999999994</v>
-      </c>
-      <c r="G2">
-        <f>D2*0.0254</f>
-        <v>0.52069999999999994</v>
-      </c>
-      <c r="H2">
-        <f>E2*0.0254</f>
-        <v>0.17779999999999999</v>
-      </c>
-      <c r="I2">
-        <f>F2*G2*H2</f>
-        <v>4.8206645521999984E-2</v>
-      </c>
-      <c r="J2">
-        <f>I2*2*3</f>
-        <v>0.28923987313199989</v>
-      </c>
-      <c r="K2">
-        <f>B2*0.15</f>
-        <v>15</v>
-      </c>
-      <c r="L2">
-        <f>B2*0.1</f>
-        <v>10</v>
-      </c>
-      <c r="M2">
-        <f>IF(B2&lt;120,5,10)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="str">
-        <f>Input_Data!A3</f>
-        <v>MH-901</v>
-      </c>
-      <c r="B3">
-        <f>Input_Data!B3</f>
-        <v>150</v>
-      </c>
-      <c r="C3">
-        <f>VALUE(LEFT(Input_Data!C3,FIND(" X ",Input_Data!C3)-1))</f>
-        <v>30</v>
-      </c>
-      <c r="D3">
-        <f>VALUE(MID(Input_Data!C3,FIND(" X ",Input_Data!C3)+3,FIND(" X ",Input_Data!C3,FIND(" X ", Input_Data!C3)+1)-FIND(" X ", Input_Data!C3)-3))</f>
-        <v>18.5</v>
-      </c>
-      <c r="E3">
-        <f>VALUE(RIGHT(Input_Data!C3,LEN(Input_Data!C3)-FIND(" X ", Input_Data!C3,FIND(" X ", Input_Data!C3)+1)-2))</f>
-        <v>6.25</v>
-      </c>
-      <c r="F3">
-        <f t="shared" ref="F3:F5" si="0">C3*0.0254</f>
-        <v>0.76200000000000001</v>
-      </c>
-      <c r="G3">
-        <f t="shared" ref="G3:G5" si="1">D3*0.0254</f>
-        <v>0.46989999999999998</v>
-      </c>
-      <c r="H3">
-        <f t="shared" ref="H3:H5" si="2">E3*0.0254</f>
-        <v>0.15875</v>
-      </c>
-      <c r="I3">
-        <f t="shared" ref="I3:I5" si="3">F3*G3*H3</f>
-        <v>5.6842628249999999E-2</v>
-      </c>
-      <c r="J3">
-        <f t="shared" ref="J3:J5" si="4">I3*2*3</f>
-        <v>0.34105576949999999</v>
-      </c>
-      <c r="K3">
-        <f t="shared" ref="K3:K5" si="5">B3*0.15</f>
-        <v>22.5</v>
-      </c>
-      <c r="L3">
-        <f t="shared" ref="L3:L5" si="6">B3*0.1</f>
-        <v>15</v>
-      </c>
-      <c r="M3">
-        <f t="shared" ref="M3:M5" si="7">IF(B3&lt;120,5,10)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="str">
-        <f>Input_Data!A4</f>
-        <v>MH-805</v>
-      </c>
-      <c r="B4">
-        <f>Input_Data!B4</f>
-        <v>20.5</v>
-      </c>
-      <c r="C4">
-        <f>VALUE(LEFT(Input_Data!C4,FIND(" X ",Input_Data!C4)-1))</f>
-        <v>23</v>
-      </c>
-      <c r="D4">
-        <f>VALUE(MID(Input_Data!C4,FIND(" X ",Input_Data!C4)+3,FIND(" X ",Input_Data!C4,FIND(" X ", Input_Data!C4)+1)-FIND(" X ", Input_Data!C4)-3))</f>
-        <v>22.75</v>
-      </c>
-      <c r="E4">
-        <f>VALUE(RIGHT(Input_Data!C4,LEN(Input_Data!C4)-FIND(" X ", Input_Data!C4,FIND(" X ", Input_Data!C4)+1)-2))</f>
-        <v>4.75</v>
-      </c>
-      <c r="F4">
-        <f t="shared" si="0"/>
-        <v>0.58419999999999994</v>
-      </c>
-      <c r="G4">
-        <f t="shared" si="1"/>
-        <v>0.57784999999999997</v>
-      </c>
-      <c r="H4">
-        <f t="shared" si="2"/>
-        <v>0.12064999999999999</v>
-      </c>
-      <c r="I4">
-        <f t="shared" si="3"/>
-        <v>4.0729023380499989E-2</v>
-      </c>
-      <c r="J4">
-        <f t="shared" si="4"/>
-        <v>0.24437414028299992</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="5"/>
-        <v>3.0749999999999997</v>
-      </c>
-      <c r="L4">
-        <f t="shared" si="6"/>
-        <v>2.0500000000000003</v>
-      </c>
-      <c r="M4">
-        <f t="shared" si="7"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="str">
+    <row r="5">
+      <c r="A5">
         <f>Input_Data!A5</f>
-        <v>MH-11500</v>
-      </c>
-      <c r="B5">
-        <f>Input_Data!B5</f>
+        <v/>
+      </c>
+      <c r="B5" t="n">
         <v>163</v>
       </c>
-      <c r="C5">
-        <f>VALUE(LEFT(Input_Data!C5,FIND(" X ",Input_Data!C5)-1))</f>
+      <c r="C5" t="n">
         <v>18</v>
       </c>
-      <c r="D5">
-        <f>VALUE(MID(Input_Data!C5,FIND(" X ",Input_Data!C5)+3,FIND(" X ",Input_Data!C5,FIND(" X ", Input_Data!C5)+1)-FIND(" X ", Input_Data!C5)-3))</f>
+      <c r="D5" t="n">
         <v>81</v>
       </c>
-      <c r="E5">
-        <f>VALUE(RIGHT(Input_Data!C5,LEN(Input_Data!C5)-FIND(" X ", Input_Data!C5,FIND(" X ", Input_Data!C5)+1)-2))</f>
+      <c r="E5" t="n">
         <v>14.5</v>
       </c>
-      <c r="F5">
-        <f t="shared" si="0"/>
+      <c r="F5" t="n">
         <v>0.4572</v>
       </c>
-      <c r="G5">
-        <f t="shared" si="1"/>
-        <v>2.0573999999999999</v>
-      </c>
-      <c r="H5">
-        <f t="shared" si="2"/>
-        <v>0.36829999999999996</v>
-      </c>
-      <c r="I5">
-        <f t="shared" si="3"/>
-        <v>0.34643892002399995</v>
-      </c>
-      <c r="J5">
-        <f t="shared" si="4"/>
-        <v>2.0786335201439998</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="5"/>
+      <c r="G5" t="n">
+        <v>2.0574</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.346438920024</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.078633520144</v>
+      </c>
+      <c r="K5" t="n">
         <v>24.45</v>
       </c>
-      <c r="L5">
-        <f t="shared" si="6"/>
+      <c r="L5" t="n">
         <v>16.3</v>
       </c>
-      <c r="M5">
-        <f t="shared" si="7"/>
+      <c r="M5" t="n">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78DAF417-1789-4A1B-8978-5C83A812A31F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="10.58203125" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" customWidth="1"/>
-    <col min="3" max="3" width="11.75" customWidth="1"/>
+    <col width="10.58203125" customWidth="1" min="1" max="1"/>
+    <col width="11.6640625" customWidth="1" min="2" max="2"/>
+    <col width="11.75" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" t="s">
-        <v>31</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Selling Price</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Buying Price</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="str">
+    <row r="2">
+      <c r="A2">
         <f>Calculations!A2</f>
-        <v>MH-107</v>
-      </c>
-      <c r="B2">
-        <f>Calculations!B2</f>
+        <v/>
+      </c>
+      <c r="B2" t="n">
         <v>100</v>
       </c>
-      <c r="C2" s="16">
-        <f>Calculations!B2 -( Calculations!B2*0.15)-Calculations!K2-Calculations!L2-Calculations!M2-Calculations!J2</f>
-        <v>54.710760126868003</v>
+      <c r="C2" s="19" t="n">
+        <v>69.710760126868</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="str">
+    <row r="3">
+      <c r="A3">
         <f>Calculations!A3</f>
-        <v>MH-901</v>
-      </c>
-      <c r="B3">
-        <f>Calculations!B3</f>
+        <v/>
+      </c>
+      <c r="B3" t="n">
         <v>150</v>
       </c>
-      <c r="C3" s="16">
-        <f>Calculations!B3 -( Calculations!B3*0.15)-Calculations!K3-Calculations!L3-Calculations!M3-Calculations!J3</f>
-        <v>79.658944230499998</v>
+      <c r="C3" s="19" t="n">
+        <v>102.1589442305</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="str">
+    <row r="4">
+      <c r="A4">
         <f>Calculations!A4</f>
-        <v>MH-805</v>
-      </c>
-      <c r="B4">
-        <f>Calculations!B4</f>
+        <v/>
+      </c>
+      <c r="B4" t="n">
         <v>20.5</v>
       </c>
-      <c r="C4" s="16">
-        <f>Calculations!B4 -( Calculations!B4*0.15)-Calculations!K4-Calculations!L4-Calculations!M4-Calculations!J4</f>
-        <v>7.0556258597170007</v>
+      <c r="C4" s="19" t="n">
+        <v>10.130625859717</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="str">
+    <row r="5">
+      <c r="A5">
         <f>Calculations!A5</f>
-        <v>MH-11500</v>
-      </c>
-      <c r="B5">
-        <f>Calculations!B5</f>
+        <v/>
+      </c>
+      <c r="B5" t="n">
         <v>163</v>
       </c>
-      <c r="C5" s="16">
-        <f>Calculations!B5 -( Calculations!B5*0.15)-Calculations!K5-Calculations!L5-Calculations!M5-Calculations!J5</f>
-        <v>85.721366479856016</v>
+      <c r="C5" s="19" t="n">
+        <v>110.171366479856</v>
       </c>
     </row>
   </sheetData>
